--- a/docs/pension_data_combined_2026-09-10.xlsx
+++ b/docs/pension_data_combined_2026-09-10.xlsx
@@ -1228,7 +1228,7 @@
         <v>1.144</v>
       </c>
       <c r="D48" t="n">
-        <v>3923523.09</v>
+        <v>4061522.58</v>
       </c>
     </row>
     <row r="49">
@@ -1246,7 +1246,7 @@
         <v>2.1437</v>
       </c>
       <c r="D49" t="n">
-        <v>69805093.28</v>
+        <v>70948851.06</v>
       </c>
     </row>
     <row r="50">
@@ -1264,7 +1264,7 @@
         <v>2.163</v>
       </c>
       <c r="D50" t="n">
-        <v>227433382.97</v>
+        <v>229651736.9</v>
       </c>
     </row>
     <row r="51">
@@ -1282,7 +1282,7 @@
         <v>2.181</v>
       </c>
       <c r="D51" t="n">
-        <v>348252258.32</v>
+        <v>350864417.6</v>
       </c>
     </row>
     <row r="52">
@@ -1300,7 +1300,7 @@
         <v>2.1869</v>
       </c>
       <c r="D52" t="n">
-        <v>425343559.99</v>
+        <v>427653194.2</v>
       </c>
     </row>
     <row r="53">
@@ -1318,7 +1318,7 @@
         <v>1.9608</v>
       </c>
       <c r="D53" t="n">
-        <v>392771783.43</v>
+        <v>394937498.6</v>
       </c>
     </row>
     <row r="54">
@@ -1336,7 +1336,7 @@
         <v>1.527</v>
       </c>
       <c r="D54" t="n">
-        <v>316596028.73</v>
+        <v>318295031.6</v>
       </c>
     </row>
     <row r="55">
@@ -1354,7 +1354,7 @@
         <v>1.1874</v>
       </c>
       <c r="D55" t="n">
-        <v>59068234.98</v>
+        <v>59159832.74</v>
       </c>
     </row>
   </sheetData>

--- a/docs/pension_data_combined_2026-09-10.xlsx
+++ b/docs/pension_data_combined_2026-09-10.xlsx
@@ -1224,9 +1224,6 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>1.144</v>
-      </c>
       <c r="D48" t="n">
         <v>4061522.58</v>
       </c>

--- a/docs/pension_data_combined_2026-09-10.xlsx
+++ b/docs/pension_data_combined_2026-09-10.xlsx
@@ -1224,6 +1224,9 @@
           <t>2026-09-10</t>
         </is>
       </c>
+      <c r="C48" t="n">
+        <v>1.144</v>
+      </c>
       <c r="D48" t="n">
         <v>4061522.58</v>
       </c>

--- a/docs/pension_data_combined_2026-09-10.xlsx
+++ b/docs/pension_data_combined_2026-09-10.xlsx
@@ -1281,9 +1281,6 @@
       <c r="C51" t="n">
         <v>2.181</v>
       </c>
-      <c r="D51" t="n">
-        <v>350864417.6</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
